--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92554690051</v>
+        <v>46157.93110915257</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110915257</v>
+        <v>46157.93134793428</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93134793428</v>
+        <v>46157.93382462604</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93382462604</v>
+        <v>46157.9369427606</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9369427606</v>
+        <v>46158.28204344901</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28204344901</v>
+        <v>46158.29651343418</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29651343418</v>
+        <v>46158.29806212167</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806212167</v>
+        <v>46158.33369330718</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33369330718</v>
+        <v>46158.37220953939</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37220953939</v>
+        <v>46158.37274917444</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
